--- a/artfynd/A 186-2026 artfynd.xlsx
+++ b/artfynd/A 186-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91261663</v>
+        <v>131602606</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Linderåsen, ostbranten, Gstr</t>
+          <t>Linderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576052</v>
+        <v>575521</v>
       </c>
       <c r="R2" t="n">
-        <v>6712838</v>
+        <v>6712407</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-06-13</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-06-13</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,28 +767,125 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skog, barrskog, blandbarr, 200-årig skog med grova tallar,  delvis bergbrant, nyckelbiotopkaraktär</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 309026L</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>91261663</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Linderåsen, ostbranten, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>576052</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6712838</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2010-06-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2010-06-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skog, barrskog, blandbarr, 200-årig skog med grova tallar,  delvis bergbrant, nyckelbiotopkaraktär</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 309026L</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Peter Ståhl</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Peter Ståhl</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>

--- a/artfynd/A 186-2026 artfynd.xlsx
+++ b/artfynd/A 186-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602606</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91261663</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>